--- a/output/pdf_financials_xlsx/NOVA.xlsx
+++ b/output/pdf_financials_xlsx/NOVA.xlsx
@@ -3981,28 +3981,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.037654</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.124556</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.224984</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.578182</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.681661</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.036076</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.14424</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.262167</v>
       </c>
     </row>
     <row r="93">
@@ -6407,7 +6407,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7229,7 +7233,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9759,7 +9767,11 @@
           <t>$                      $                                                    Reserves</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -10465,7 +10477,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -13480,7 +13496,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOVA.xlsx
+++ b/output/pdf_financials_xlsx/NOVA.xlsx
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.236598</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.014163</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.957103</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.8674230000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.953389</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.9604510000000001</v>
@@ -1986,19 +1986,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.236598</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.014163</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.957103</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.294</v>
+        <v>1.161423</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.204</v>
+        <v>1.157389</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1.155451</v>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">

--- a/output/pdf_financials_xlsx/NOVA.xlsx
+++ b/output/pdf_financials_xlsx/NOVA.xlsx
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.3224</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.0646</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.409248</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>1.328702</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -20223,7 +20223,11 @@
           <t>Issuance of common shares for cash, net of issuance costs</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>0.3224</v>
       </c>

--- a/output/pdf_financials_xlsx/NOVA.xlsx
+++ b/output/pdf_financials_xlsx/NOVA.xlsx
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.332666</v>
+        <v>0.364274</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.249117</v>
+        <v>0.282076</v>
       </c>
     </row>
     <row r="8">
@@ -4257,19 +4257,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003944</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014382</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003894</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.046711</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024749</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.026301</v>
@@ -4427,19 +4427,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.010817</v>
+        <v>0.006873</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.003737</v>
+        <v>-0.010645</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.009129</v>
+        <v>0.005235</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.147105</v>
+        <v>-0.193816</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.131945</v>
+        <v>0.107196</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.111571</v>
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001413</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.057336</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001413</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>-0.257813</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.726221</v>
+        <v>-0.727634</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.569271</v>
@@ -5505,7 +5505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M286"/>
+  <dimension ref="A1:M287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17293,10 +17293,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K201" s="5" t="n">
+        <v>-1.248504</v>
       </c>
       <c r="L201" s="5" t="n">
         <v>-0.347845</v>
@@ -17411,10 +17409,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K203" s="5" t="n">
+        <v>-0.5</v>
       </c>
       <c r="L203" s="5" t="n">
         <v>0.5</v>
@@ -17476,10 +17472,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K204" s="5" t="n">
+        <v>-1.848504</v>
       </c>
       <c r="L204" s="5" t="n">
         <v>0.154732</v>
@@ -17535,10 +17529,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K205" s="5" t="n">
+        <v>2.4</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -17600,10 +17592,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K206" s="5" t="n">
+        <v>-0.057336</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -17773,10 +17763,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K209" s="5" t="n">
+        <v>-0.075111</v>
       </c>
       <c r="L209" s="5" t="n">
         <v>-0.442619</v>
@@ -18011,10 +17999,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Items not affecting cash used in operations</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>February 29, 2024 February</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -18044,15 +18036,13 @@
         </is>
       </c>
       <c r="J214" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.343</v>
       </c>
       <c r="K214" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.165</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>-0.178</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
@@ -18073,7 +18063,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Accrued interest</t>
+          <t>Recovery of flow-through share premium liabilities</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -18082,29 +18072,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F215" s="5" t="n">
-        <v>0.001745</v>
-      </c>
-      <c r="G215" s="5" t="n">
-        <v>0.001943</v>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>-0.185</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>-0.3</v>
       </c>
       <c r="J215" s="5" t="n">
-        <v>0.001668</v>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.155338</v>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>-0.011044</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -18130,7 +18118,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Unrealized loss on marketable securities</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -18149,28 +18137,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J216" s="5" t="n">
-        <v>-7e-06</v>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H216" s="5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -18186,12 +18168,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Items not affecting cash used in operations</t>
+          <t>Cash flows provided by (used in) investing activities</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Funds received (paid for) reclamation bond</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -18220,16 +18202,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J217" s="5" t="n">
-        <v>0.343</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K217" s="5" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.1</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>0.002577</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -18245,12 +18227,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Items not affecting cash used in operations</t>
+          <t>Change in deferred exploration costs included in accounts</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Realized loss on sale of marketable securities</t>
+          <t>Change in deferred exploration costs included in accounts payable and amounts due to related parties $</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -18280,17 +18262,13 @@
         </is>
       </c>
       <c r="J218" s="5" t="n">
-        <v>0.00923</v>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.086081</v>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>-0.085434</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>0.007369</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -18304,14 +18282,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Items not affecting cash used in operations</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Recovery of flow-through share premium liabilities</t>
+          <t>February 29, 2024 February</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -18330,17 +18304,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" s="5" t="n">
-        <v>-0.185</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>-0.3</v>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J219" s="5" t="n">
-        <v>-0.155338</v>
+        <v>0.002023</v>
       </c>
       <c r="K219" s="5" t="n">
-        <v>-0.011044</v>
+        <v>2.8e-05</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -18361,12 +18339,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets, net of tax credits</t>
+          <t>Accrued interest</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -18375,25 +18353,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F220" s="5" t="n">
+        <v>0.001745</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>-0.025265</v>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>-1.098729</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>-1.956964</v>
+        <v>0.001943</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J220" s="5" t="n">
-        <v>-2.412325</v>
-      </c>
-      <c r="K220" s="5" t="n">
-        <v>-1.248504</v>
+        <v>0.001668</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -18414,12 +18396,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Funds paid for reclamation bond</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -18438,17 +18420,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>-0.023755</v>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J221" s="5" t="n">
-        <v>-0.037208</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>-0.1</v>
+        <v>-7e-06</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -18469,12 +18457,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Short-term investment</t>
+          <t>Realized loss on sale of marketable securities</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -18503,13 +18491,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>-0.5</v>
+      <c r="J222" s="5" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -18535,7 +18523,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Acquisition of equipment</t>
+          <t>Exploration and evaluation assets, net of tax credits</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -18549,28 +18537,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G223" s="5" t="n">
+        <v>-0.025265</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-1.098729</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>-1.956964</v>
       </c>
       <c r="J223" s="5" t="n">
-        <v>-0.001413</v>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.412325</v>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>-1.248504</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -18596,7 +18576,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cash received from sale of equity investments</t>
+          <t>Funds paid for reclamation bond</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -18615,23 +18595,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>-0.023755</v>
       </c>
       <c r="J224" s="5" t="n">
-        <v>0.05877</v>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.037208</v>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>-0.1</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -18657,34 +18631,42 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="n">
-        <v>-0.105612</v>
-      </c>
-      <c r="F225" s="5" t="n">
-        <v>-0.280387</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>-0.025265</v>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>-1.081729</v>
-      </c>
-      <c r="I225" s="5" t="n">
-        <v>-1.980719</v>
-      </c>
-      <c r="J225" s="5" t="n">
-        <v>-2.392176</v>
+          <t>Short-term investment</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>-1.848504</v>
+        <v>-0.5</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -18705,15 +18687,19 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Issuance of shares for cash, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Acquisition of equipment</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -18729,17 +18715,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H226" s="5" t="n">
-        <v>1.328702</v>
-      </c>
-      <c r="I226" s="5" t="n">
-        <v>2.226801</v>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J226" s="5" t="n">
-        <v>3.170377</v>
-      </c>
-      <c r="K226" s="5" t="n">
-        <v>2.342664</v>
+        <v>-0.001413</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -18760,12 +18752,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Issuance of shares on exercise of options</t>
+          <t>Cash received from sale of equity investments</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -18784,14 +18776,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" s="5" t="n">
-        <v>0.040562</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>0.0965</v>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J227" s="5" t="n">
-        <v>0.07675</v>
+        <v>0.05877</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -18817,47 +18813,39 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Repayment of related party loan</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="n">
+        <v>-0.105612</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>-0.280387</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>-0.025265</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>-1.081729</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>-1.980719</v>
       </c>
       <c r="J228" s="5" t="n">
-        <v>-0.121668</v>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.392176</v>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>-1.848504</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -18883,14 +18871,10 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Issuance of shares for cash, net of issuance costs</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -18906,21 +18890,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H229" s="5" t="n">
+        <v>1.328702</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>2.226801</v>
       </c>
       <c r="J229" s="5" t="n">
-        <v>0.007062</v>
+        <v>3.170377</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>-0.075111</v>
+        <v>2.342664</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -18941,12 +18921,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Change in deferred exploration costs included in accounts</t>
+          <t>Cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Change in deferred exploration costs included in accounts payable and amounts due to related parties $</t>
+          <t>Issuance of shares on exercise of options</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -18965,21 +18945,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H230" s="5" t="n">
+        <v>0.040562</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>0.0965</v>
       </c>
       <c r="J230" s="5" t="n">
-        <v>0.086081</v>
-      </c>
-      <c r="K230" s="5" t="n">
-        <v>-0.085434</v>
+        <v>0.07675</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -18998,10 +18976,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Cash flows provided by financing activities</t>
+        </is>
+      </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>YEAR ENDED FEBRUARY</t>
+          <t>Repayment of related party loan</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -19020,14 +19002,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="I231" s="5" t="n">
-        <v>0.002023</v>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J231" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>-0.121668</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -19051,13 +19037,21 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Cash flows provided by financing activities</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>February 28, 2023 February</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -19078,16 +19072,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I232" s="5" t="n">
-        <v>0.002022</v>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J232" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007062</v>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>-0.075111</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -19106,14 +19100,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Items not affecting cash used in operations</t>
-        </is>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities</t>
+          <t>YEAR ENDED FEBRUARY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -19132,18 +19122,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="J233" s="5" t="n">
-        <v>0.00923</v>
+        <v>2.8e-05</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -19167,34 +19153,38 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>February 28, 2023 February</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" s="5" t="n">
-        <v>-0.003944</v>
-      </c>
-      <c r="F234" s="5" t="n">
-        <v>-0.014382</v>
-      </c>
-      <c r="G234" s="5" t="n">
-        <v>-0.003894</v>
-      </c>
-      <c r="H234" s="5" t="n">
-        <v>-0.046711</v>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I234" s="5" t="n">
-        <v>-0.024749</v>
+        <v>0.002022</v>
       </c>
       <c r="J234" s="5" t="n">
-        <v>-0.026301</v>
+        <v>2.8e-05</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -19220,19 +19210,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Realized gain on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -19248,14 +19234,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H235" s="5" t="n">
-        <v>-0.08968</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>0.085966</v>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J235" s="5" t="n">
-        <v>0.007062</v>
+        <v>0.00923</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -19281,34 +19271,36 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="n">
+        <v>-0.003944</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.236598</v>
+        <v>-0.014382</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>0.014163</v>
+        <v>-0.003894</v>
       </c>
       <c r="H236" s="5" t="n">
-        <v>0.957103</v>
+        <v>-0.046711</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>0.8674230000000001</v>
+        <v>-0.024749</v>
       </c>
       <c r="J236" s="5" t="n">
-        <v>0.953389</v>
+        <v>-0.026301</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -19339,27 +19331,37 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Cash, ending $</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" s="5" t="n">
-        <v>0.236598</v>
-      </c>
-      <c r="F237" s="5" t="n">
-        <v>0.014163</v>
-      </c>
-      <c r="G237" s="5" t="n">
-        <v>0.957103</v>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H237" s="5" t="n">
-        <v>0.8674230000000001</v>
+        <v>-0.08968</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>0.953389</v>
+        <v>0.085966</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.9604510000000001</v>
+        <v>0.007062</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -19385,12 +19387,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Shares issued for debt with related party $</t>
+          <t>Cash, beginning</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -19399,28 +19401,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F238" s="5" t="n">
+        <v>0.236598</v>
+      </c>
+      <c r="G238" s="5" t="n">
+        <v>0.014163</v>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>0.957103</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.8674230000000001</v>
+      </c>
+      <c r="J238" s="5" t="n">
+        <v>0.953389</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -19446,42 +19440,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Promissory note issued for property $</t>
+          <t>Cash, ending $</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E239" s="5" t="n">
+        <v>0.236598</v>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>0.014163</v>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>0.957103</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>0.8674230000000001</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.953389</v>
+      </c>
+      <c r="J239" s="5" t="n">
+        <v>0.9604510000000001</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -19507,12 +19491,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Deferred exploration costs included in accounts payable and</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Deferred exploration costs included in accounts payable and amounts due to related parties $</t>
+          <t>Shares issued for debt with related party $</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -19536,13 +19520,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J240" s="5" t="n">
-        <v>0.086081</v>
+      <c r="I240" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -19566,10 +19550,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Non-cash transactions</t>
+        </is>
+      </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>February 28, 2022 February</t>
+          <t>Promissory note issued for property $</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -19588,11 +19576,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="5" t="n">
-        <v>0.002021</v>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I241" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>0.12</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -19623,12 +19613,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Items not affecting cash used in operations</t>
+          <t>Deferred exploration costs included in accounts payable and</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Options granted for services</t>
+          <t>Deferred exploration costs included in accounts payable and amounts due to related parties $</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -19647,16 +19637,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="5" t="n">
-        <v>0.006523</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>0.094988</v>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="n">
+        <v>0.086081</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -19680,14 +19672,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Items not affecting cash used in operations</t>
-        </is>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of debt with related parties</t>
+          <t>February 28, 2022 February</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -19707,12 +19695,10 @@
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -19748,7 +19734,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities</t>
+          <t>Options granted for services</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -19768,10 +19754,10 @@
         </is>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.114</v>
+        <v>0.006523</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>0.09</v>
+        <v>0.094988</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -19807,7 +19793,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Loss on sale of mineral property</t>
+          <t>Gain on forgiveness of debt with related parties</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -19827,7 +19813,7 @@
         </is>
       </c>
       <c r="H245" s="5" t="n">
-        <v>0.00179</v>
+        <v>-0.015</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19863,12 +19849,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Proceeds received on transfer of reclamation bond</t>
+          <t>Loss on sale of mineral property</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -19888,7 +19874,7 @@
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.042</v>
+        <v>0.00179</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19924,29 +19910,37 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
+          <t>Proceeds received on transfer of reclamation bond</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="E247" s="5" t="n">
-        <v>0.040208</v>
-      </c>
-      <c r="F247" s="5" t="n">
-        <v>0.033512</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>-0.024879</v>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H247" s="5" t="n">
-        <v>0.022877</v>
-      </c>
-      <c r="I247" s="5" t="n">
-        <v>0.055772</v>
+        <v>0.042</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -19977,37 +19971,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Shares received on sale of exploration and evaluation asset $</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E248" s="5" t="n">
+        <v>0.040208</v>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.033512</v>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>-0.024879</v>
       </c>
       <c r="H248" s="5" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022877</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>0.055772</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -20043,7 +20029,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Debt forgiveness $</t>
+          <t>Shares received on sale of exploration and evaluation asset $</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -20063,7 +20049,7 @@
         </is>
       </c>
       <c r="H249" s="5" t="n">
-        <v>0.011589</v>
+        <v>0.408</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -20097,10 +20083,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Non-cash transactions</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>February 28, 2021 February</t>
+          <t>Debt forgiveness $</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -20114,11 +20104,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G250" s="5" t="n">
-        <v>0.00202</v>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>0.011589</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -20152,14 +20144,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Items not affecting cash used in operations</t>
-        </is>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Reversal of flow-through share premium</t>
+          <t>February 28, 2021 February</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -20173,13 +20161,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G251" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>-0.185</v>
+        <v>2.9e-05</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -20215,30 +20201,32 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Cash flows provided by financing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Issuance of common shares for cash, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
-      <c r="E252" s="5" t="n">
-        <v>0.3224</v>
-      </c>
-      <c r="F252" s="5" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="G252" s="5" t="n">
-        <v>1.409248</v>
+          <t>Reversal of flow-through share premium</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H252" s="5" t="n">
-        <v>1.328702</v>
+        <v>-0.185</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -20279,25 +20267,25 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of options</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of common shares for cash, net of issuance costs</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>0.0646</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>0.041</v>
+        <v>1.409248</v>
       </c>
       <c r="H253" s="5" t="n">
-        <v>0.040562</v>
+        <v>1.328702</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20338,7 +20326,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of warrants</t>
+          <t>Issuance of common shares on exercise of options</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -20352,13 +20340,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G254" s="5" t="n">
+        <v>0.041</v>
       </c>
       <c r="H254" s="5" t="n">
-        <v>0.04497</v>
+        <v>0.040562</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20399,7 +20385,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Loans with related parties</t>
+          <t>Issuance of common shares on exercise of warrants</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -20408,16 +20394,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F255" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G255" s="5" t="n">
-        <v>-0.113688</v>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>0.04497</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20458,25 +20446,25 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E256" s="5" t="n">
-        <v>0.236598</v>
+          <t>Loans with related parties</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.222435</v>
+        <v>0.11</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>0.94294</v>
-      </c>
-      <c r="H256" s="5" t="n">
-        <v>-0.08968</v>
+        <v>-0.113688</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20512,32 +20500,30 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Increase (decrease) in cash</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
-        <v>-0.105612</v>
+        <v>0.236598</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>-0.236452</v>
+        <v>-0.222435</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>-0.025265</v>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.94294</v>
+      </c>
+      <c r="H257" s="5" t="n">
+        <v>-0.08968</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -20578,22 +20564,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Funds paid for security bond</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>-0.105612</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.236452</v>
+      </c>
+      <c r="G258" s="5" t="n">
+        <v>-0.025265</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -20639,21 +20625,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant, and equipment</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
+          <t>Funds paid for security bond</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F259" s="5" t="n">
-        <v>-0.001935</v>
+        <v>-0.042</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -20699,20 +20681,26 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Period from July</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Year ended</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" s="5" t="n">
-        <v>0.002017</v>
+          <t>Acquisition of property, plant, and equipment</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F260" s="5" t="n">
-        <v>7e-06</v>
+        <v>-0.001935</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -20763,15 +20751,15 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2019 February</t>
+          <t>Year ended</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" s="5" t="n">
-        <v>0.002018</v>
+        <v>0.002017</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>7e-06</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -20817,24 +20805,20 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
+          <t>Period from July</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>2019 February</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" s="5" t="n">
-        <v>-0.047271</v>
+        <v>0.002018</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>-0.179313</v>
+        <v>2.8e-05</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -20880,22 +20864,24 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Items not affecting cash used in operations</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Shares issued for service</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.047271</v>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>-0.179313</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -20941,26 +20927,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Items not affecting cash used in operations</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>-0.001935</v>
+          <t>Shares issued for service</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -21001,22 +20983,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Advertising, promotion and investor relations 11 $</t>
+          <t>Acquisition of property, plant and equipment</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21024,10 +21006,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F265" s="5" t="n">
+        <v>-0.001935</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -21054,11 +21034,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L265" s="5" t="n">
-        <v>0.117764</v>
-      </c>
-      <c r="M265" s="5" t="n">
-        <v>0.10481</v>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -21074,12 +21058,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Advertising, promotion and investor relations 11 $</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21118,10 +21102,10 @@
         </is>
       </c>
       <c r="L266" s="5" t="n">
-        <v>0.000327</v>
+        <v>0.117764</v>
       </c>
       <c r="M266" s="5" t="n">
-        <v>7.4e-05</v>
+        <v>0.10481</v>
       </c>
     </row>
     <row r="267">
@@ -21137,12 +21121,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Consulting fees 11</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -21181,10 +21165,10 @@
         </is>
       </c>
       <c r="L267" s="5" t="n">
-        <v>0.161986</v>
+        <v>0.000327</v>
       </c>
       <c r="M267" s="5" t="n">
-        <v>0.088731</v>
+        <v>7.4e-05</v>
       </c>
     </row>
     <row r="268">
@@ -21200,10 +21184,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Office expenses</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Consulting fees 11</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -21240,10 +21228,10 @@
         </is>
       </c>
       <c r="L268" s="5" t="n">
-        <v>0.031608</v>
+        <v>0.161986</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>0.032959</v>
+        <v>0.088731</v>
       </c>
     </row>
     <row r="269">
@@ -21259,10 +21247,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Project investigation costs 8,11</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Office expenses</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -21299,10 +21291,10 @@
         </is>
       </c>
       <c r="L269" s="5" t="n">
-        <v>0.068675</v>
+        <v>0.031608</v>
       </c>
       <c r="M269" s="5" t="n">
-        <v>0.057448</v>
+        <v>0.032959</v>
       </c>
     </row>
     <row r="270">
@@ -21318,14 +21310,10 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Professional fees 11</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Project investigation costs 8,11</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -21362,10 +21350,10 @@
         </is>
       </c>
       <c r="L270" s="5" t="n">
-        <v>0.164131</v>
+        <v>0.068675</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>0.134232</v>
+        <v>0.057448</v>
       </c>
     </row>
     <row r="271">
@@ -21381,12 +21369,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Professional fees 11</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -21425,10 +21413,10 @@
         </is>
       </c>
       <c r="L271" s="5" t="n">
-        <v>0.052916</v>
+        <v>0.164131</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>0.055576</v>
+        <v>0.134232</v>
       </c>
     </row>
     <row r="272">
@@ -21444,12 +21432,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Salaries and wages 11</t>
+          <t>Regulatory fees</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -21487,13 +21475,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L272" s="5" t="n">
+        <v>0.052916</v>
       </c>
       <c r="M272" s="5" t="n">
-        <v>0.098035</v>
+        <v>0.055576</v>
       </c>
     </row>
     <row r="273">
@@ -21509,10 +21495,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Share-based compensation 10,11</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Salaries and wages 11</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -21548,11 +21538,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n">
-        <v>0.108007</v>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0.107095</v>
+        <v>0.098035</v>
       </c>
     </row>
     <row r="274">
@@ -21568,7 +21560,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Travel, meals, and entertainment</t>
+          <t>Share-based compensation 10,11</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -21608,10 +21600,10 @@
         </is>
       </c>
       <c r="L274" s="5" t="n">
-        <v>0.042411</v>
+        <v>0.108007</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.019287</v>
+        <v>0.107095</v>
       </c>
     </row>
     <row r="275">
@@ -21627,7 +21619,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets 8</t>
+          <t>Travel, meals, and entertainment</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -21667,10 +21659,10 @@
         </is>
       </c>
       <c r="L275" s="5" t="n">
-        <v>0.8772489999999999</v>
+        <v>0.042411</v>
       </c>
       <c r="M275" s="5" t="n">
-        <v>0.08788799999999999</v>
+        <v>0.019287</v>
       </c>
     </row>
     <row r="276">
@@ -21686,14 +21678,10 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Write-off of exploration and evaluation assets 8</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -21730,10 +21718,10 @@
         </is>
       </c>
       <c r="L276" s="5" t="n">
-        <v>1.625074</v>
+        <v>0.8772489999999999</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>0.786135</v>
+        <v>0.08788799999999999</v>
       </c>
     </row>
     <row r="277">
@@ -21744,15 +21732,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities 9</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -21789,10 +21781,10 @@
         </is>
       </c>
       <c r="L277" s="5" t="n">
-        <v>-0.005</v>
+        <v>1.625074</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.018</v>
+        <v>0.786135</v>
       </c>
     </row>
     <row r="278">
@@ -21808,7 +21800,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Interest earned 6</t>
+          <t>Unrealized gain (loss) on marketable securities 9</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -21848,10 +21840,10 @@
         </is>
       </c>
       <c r="L278" s="5" t="n">
-        <v>0.045139</v>
+        <v>-0.005</v>
       </c>
       <c r="M278" s="5" t="n">
-        <v>0.003574</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="279">
@@ -21867,14 +21859,10 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Net loss for the year before income taxes</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Interest earned 6</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -21911,10 +21899,10 @@
         </is>
       </c>
       <c r="L279" s="5" t="n">
-        <v>-1.584935</v>
+        <v>0.045139</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>-0.764561</v>
+        <v>0.003574</v>
       </c>
     </row>
     <row r="280">
@@ -21930,10 +21918,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Income tax recovery – deferred 12</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Net loss for the year before income taxes</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -21970,12 +21962,10 @@
         </is>
       </c>
       <c r="L280" s="5" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.584935</v>
+      </c>
+      <c r="M280" s="5" t="n">
+        <v>-0.764561</v>
       </c>
     </row>
     <row r="281">
@@ -21991,14 +21981,10 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Income tax recovery – deferred 12</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -22035,10 +22021,12 @@
         </is>
       </c>
       <c r="L281" s="5" t="n">
-        <v>-1.406935</v>
-      </c>
-      <c r="M281" s="5" t="n">
-        <v>-0.764561</v>
+        <v>0.178</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -22054,12 +22042,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net and comprehensive loss $</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -22098,10 +22086,10 @@
         </is>
       </c>
       <c r="L282" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.406935</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.764561</v>
       </c>
     </row>
     <row r="283">
@@ -22112,15 +22100,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding; basic and diluted</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -22157,10 +22149,10 @@
         </is>
       </c>
       <c r="L283" s="5" t="n">
-        <v>46.473904</v>
+        <v>-3e-08</v>
       </c>
       <c r="M283" s="5" t="n">
-        <v>48.872566</v>
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="284">
@@ -22171,12 +22163,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Total 11,417,008 23,125 108,164 (1,406,935) 10,141,362 573,960 (40,578) 22,500 107,095 (764,561)</t>
+          <t>Weighted average number of common shares outstanding; basic and diluted</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -22216,10 +22208,10 @@
         </is>
       </c>
       <c r="L284" s="5" t="n">
-        <v>3e-06</v>
+        <v>46.473904</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>10.039778</v>
+        <v>48.872566</v>
       </c>
     </row>
     <row r="285">
@@ -22230,12 +22222,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>$                $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                statements.</t>
+          <t>|</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>-  -                      10,832 - -  -                                                                                                                                                                financial                                                                                        1,036,076               108,164                                 1,144,240                                    107,095                   1,262,167                                                                 Reserves these</t>
+          <t>Total 11,417,008 23,125 108,164 (1,406,935) 10,141,362 573,960 (40,578) 22,500 107,095 (764,561)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -22275,10 +22267,10 @@
         </is>
       </c>
       <c r="L285" s="5" t="n">
-        <v>0.0225</v>
+        <v>3e-06</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>0.023125</v>
+        <v>10.039778</v>
       </c>
     </row>
     <row r="286">
@@ -22294,7 +22286,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$ integral - - -</t>
+          <t>-  -                      10,832 - -  -                                                                                                                                                                financial                                                                                        1,036,076               108,164                                 1,144,240                                    107,095                   1,262,167                                                                 Reserves these</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -22333,12 +22325,71 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
+      <c r="L286" s="5" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="M286" s="5" t="n">
+        <v>0.023125</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>$                $                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                statements.</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>$ integral - - -</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
